--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -5,28 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF608DA-082E-43AE-BC44-0F86B5AE88EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030A918A-E389-486C-8268-40B52ADD4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="746" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="746" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
-    <sheet name="составные важные" sheetId="1" r:id="rId3"/>
-    <sheet name="неизменные" sheetId="10" r:id="rId4"/>
-    <sheet name="Вездесущие слова" sheetId="4" r:id="rId5"/>
-    <sheet name="Неизменные_длинные" sheetId="6" r:id="rId6"/>
-    <sheet name="Неизменные_короткие" sheetId="9" r:id="rId7"/>
-    <sheet name="перепсиать" sheetId="8" r:id="rId8"/>
-    <sheet name="создателю ошибки" sheetId="7" r:id="rId9"/>
+    <sheet name="составные_длинные" sheetId="11" r:id="rId3"/>
+    <sheet name="составные важные" sheetId="1" r:id="rId4"/>
+    <sheet name="неизменные" sheetId="10" r:id="rId5"/>
+    <sheet name="Вездесущие слова" sheetId="4" r:id="rId6"/>
+    <sheet name="Неизменные_длинные" sheetId="6" r:id="rId7"/>
+    <sheet name="Неизменные_короткие" sheetId="9" r:id="rId8"/>
+    <sheet name="перепсиать" sheetId="8" r:id="rId9"/>
+    <sheet name="создателю ошибки" sheetId="7" r:id="rId10"/>
+    <sheet name="запятые" sheetId="12" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Неизменные_длинные!$A$1:$B$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$1:$B$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$1:$B$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Неизменные_длинные!$A$1:$B$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$1:$B$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'составные важные'!$A$1:$B$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="733">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -240,9 +242,6 @@
     <t>запомнили все</t>
   </si>
   <si>
-    <t>магии белой или черной.</t>
-  </si>
-  <si>
     <t>колдовства белого или черного</t>
   </si>
   <si>
@@ -1786,9 +1785,6 @@
   </si>
   <si>
     <t>магии белой или черной</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> колдовства чёрного или белого</t>
   </si>
   <si>
     <t>магами и колдунами</t>
@@ -2602,433 +2598,433 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3554379-2F3E-45B9-9150-AA61D6D2322E}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.89453125" customWidth="1"/>
-    <col min="2" max="2" width="42.5234375" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" customWidth="1"/>
+    <col min="2" max="2" width="42.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>243</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>245</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>248</v>
+      </c>
+      <c r="B17" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>250</v>
+      </c>
+      <c r="B18" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>247</v>
-      </c>
-      <c r="B15" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>253</v>
-      </c>
-      <c r="B16" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>249</v>
-      </c>
-      <c r="B17" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B25" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>257</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>259</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B28" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>265</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>262</v>
+      </c>
+      <c r="B30" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>261</v>
-      </c>
-      <c r="B29" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>263</v>
-      </c>
-      <c r="B30" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>267</v>
       </c>
-      <c r="B31" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" t="s">
         <v>200</v>
       </c>
-      <c r="B32" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>198</v>
-      </c>
-      <c r="B33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>202</v>
       </c>
-      <c r="B34" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>204</v>
       </c>
-      <c r="B35" t="s">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>206</v>
       </c>
-      <c r="B36" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>208</v>
       </c>
-      <c r="B37" t="s">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>216</v>
-      </c>
-      <c r="B38" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>210</v>
       </c>
-      <c r="B40" t="s">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>212</v>
       </c>
-      <c r="B41" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>320</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B42" s="1" t="s">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>317</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>318</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>330</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>318</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>319</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>331</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>323</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
+      <c r="B47" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B47" s="1" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
+      <c r="B48" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B48" s="1" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
+      <c r="B49" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
     </row>
@@ -3040,488 +3036,617 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
+  <dimension ref="A2:B18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.81640625" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>409</v>
+      </c>
+      <c r="B11" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B12" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>607</v>
+      </c>
+      <c r="B14" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>611</v>
+      </c>
+      <c r="B15" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>663</v>
+      </c>
+      <c r="B16" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="B17" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>682</v>
+      </c>
+      <c r="B18" t="s">
+        <v>683</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B26617-30D2-46AE-BC55-6342488EEBC7}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="42.90625" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A1:B64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B63"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="38.47265625" customWidth="1"/>
+    <col min="2" max="2" width="38.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="B13" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>414</v>
-      </c>
-      <c r="B14" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>217</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>218</v>
+        <v>494</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
         <v>495</v>
       </c>
-      <c r="B18" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>516</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>530</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
         <v>531</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>503</v>
+      </c>
+      <c r="B30" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>506</v>
+      </c>
+      <c r="B32" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>511</v>
+      </c>
+      <c r="B35" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>526</v>
+      </c>
+      <c r="B38" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>492</v>
+      </c>
+      <c r="B41" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>365</v>
+      </c>
+      <c r="B43" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>233</v>
+      </c>
+      <c r="B44" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>282</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>331</v>
+      </c>
+      <c r="B46" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>504</v>
-      </c>
-      <c r="B31" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>507</v>
-      </c>
-      <c r="B33" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>512</v>
-      </c>
-      <c r="B36" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>527</v>
-      </c>
-      <c r="B39" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>193</v>
-      </c>
-      <c r="B41" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>493</v>
-      </c>
-      <c r="B42" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>196</v>
-      </c>
-      <c r="B43" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>366</v>
-      </c>
-      <c r="B44" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
+      <c r="B48" t="s">
         <v>234</v>
       </c>
-      <c r="B45" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>283</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
-        <v>332</v>
-      </c>
-      <c r="B47" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>555</v>
-      </c>
-      <c r="B50" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>558</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>559</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>570</v>
+      </c>
+      <c r="B51" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B52" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="B53" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="B54" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B56" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="B57" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B58" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B59" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>657</v>
       </c>
@@ -3529,65 +3654,191 @@
         <v>658</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>659</v>
+        <v>694</v>
       </c>
       <c r="B61" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B62" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>700</v>
+        <v>719</v>
       </c>
       <c r="B63" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>721</v>
-      </c>
-      <c r="B64" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B63" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B50">
-    <sortCondition ref="A1:A50"/>
+  <autoFilter ref="A1:B62" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B49">
+    <sortCondition ref="A1:A49"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F429BA-9463-41C0-94A8-3DCD50C49D17}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="65.3671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="77.3671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="53.90625" customWidth="1"/>
+    <col min="2" max="2" width="49.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>576</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="65.36328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="77.36328125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -3595,771 +3846,597 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>633</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>635</v>
+        <v>179</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>2</v>
+        <v>306</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="2" t="s">
+      <c r="B41" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B46" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B64">
-    <sortCondition ref="A1:A64"/>
+  <autoFilter ref="A1:B60" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B62">
+    <sortCondition ref="A1:A62"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629FBABB-5E47-4235-BB5F-3D637E48298E}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="36.62890625" customWidth="1"/>
+    <col min="2" max="2" width="36.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B1" t="s">
         <v>557</v>
       </c>
-      <c r="B1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B3" t="s">
         <v>567</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>569</v>
       </c>
-      <c r="B4" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>572</v>
+      </c>
+      <c r="B5" t="s">
         <v>573</v>
       </c>
-      <c r="B5" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B6" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>627</v>
+      </c>
+      <c r="B7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>629</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>631</v>
-      </c>
-      <c r="B8" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B9" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>639</v>
+      </c>
+      <c r="B10" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>641</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>643</v>
-      </c>
-      <c r="B11" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B12" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B13" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>667</v>
+      </c>
+      <c r="B14" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>669</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>671</v>
-      </c>
-      <c r="B15" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B16" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B17" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>686</v>
+      </c>
+      <c r="B18" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>688</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>690</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>692</v>
-      </c>
-      <c r="B20" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B21" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B22" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B23" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>715</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="32.7890625" customWidth="1"/>
-    <col min="2" max="2" width="28.62890625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B4" t="s">
-        <v>377</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -4368,143 +4445,189 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3385F197-11E4-42AC-8C28-973059DAA642}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
   <dimension ref="A1:B134"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.15625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="39.734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="43.1796875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="39.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
@@ -4512,279 +4635,279 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="48" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="51" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="52" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
@@ -4792,15 +4915,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>38</v>
       </c>
@@ -4808,231 +4931,231 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B59" s="3" t="s">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>496</v>
+      </c>
+      <c r="B62" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
-        <v>497</v>
-      </c>
-      <c r="B62" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>17</v>
       </c>
@@ -5040,412 +5163,412 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B84" s="3" t="s">
+    </row>
+    <row r="85" spans="1:2" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A96" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="28.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B106" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B106" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="111" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B112" s="3" t="s">
+    </row>
+    <row r="113" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A113" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A116" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A117" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A120" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A127" s="3" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" s="3" t="s">
+      <c r="B127" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B127" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="128" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B130" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="132" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B132" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="133" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="134" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -5457,164 +5580,173 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9E41E9-C4FF-4A2E-9387-ABCBB02BFCB3}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="68.1015625" customWidth="1"/>
-    <col min="2" max="2" width="45.578125" customWidth="1"/>
+    <col min="1" max="1" width="68.08984375" customWidth="1"/>
+    <col min="2" max="2" width="45.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B1" t="s">
         <v>525</v>
       </c>
-      <c r="B1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B2" t="s">
         <v>529</v>
       </c>
-      <c r="B2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B3" t="s">
         <v>563</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>565</v>
       </c>
-      <c r="B4" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>596</v>
+      </c>
+      <c r="B5" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>598</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>600</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>602</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>604</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>606</v>
-      </c>
-      <c r="B9" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B10" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B11" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B12" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B13" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B14" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B15" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="B16" t="s">
         <v>681</v>
       </c>
-      <c r="B16" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B17" t="s">
-        <v>712</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>315</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5623,145 +5755,13 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C824A990-A8C7-4DCD-B8DB-90F433050C60}">
-  <dimension ref="A2:B18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="40.7890625" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A73F47B-F69E-46BD-BCFC-FFDDB8C8A9F5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B6" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>285</v>
-      </c>
-      <c r="B8" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>336</v>
-      </c>
-      <c r="B10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>410</v>
-      </c>
-      <c r="B11" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>412</v>
-      </c>
-      <c r="B12" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>609</v>
-      </c>
-      <c r="B14" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>613</v>
-      </c>
-      <c r="B15" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>665</v>
-      </c>
-      <c r="B16" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7" t="s">
-        <v>681</v>
-      </c>
-      <c r="B17" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>684</v>
-      </c>
-      <c r="B18" t="s">
-        <v>685</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/словари/энио.xlsx
+++ b/словари/энио.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030A918A-E389-486C-8268-40B52ADD4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79835D69-AFEA-48B9-A310-29441CFECF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="746" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="746" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые слова" sheetId="2" r:id="rId1"/>
     <sheet name="Сложные слова" sheetId="3" r:id="rId2"/>
-    <sheet name="составные_длинные" sheetId="11" r:id="rId3"/>
-    <sheet name="составные важные" sheetId="1" r:id="rId4"/>
+    <sheet name="составные важные" sheetId="1" r:id="rId3"/>
+    <sheet name="составные_длинные" sheetId="11" r:id="rId4"/>
     <sheet name="неизменные" sheetId="10" r:id="rId5"/>
     <sheet name="Вездесущие слова" sheetId="4" r:id="rId6"/>
     <sheet name="Неизменные_длинные" sheetId="6" r:id="rId7"/>
@@ -26,9 +26,9 @@
     <sheet name="запятые" sheetId="12" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Неизменные_длинные!$A$1:$B$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$1:$B$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'составные важные'!$A$1:$B$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Неизменные_длинные!$A$1:$B$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сложные слова'!$A$1:$B$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'составные важные'!$A$1:$B$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="730">
   <si>
     <t>некую свою гипотезу</t>
   </si>
@@ -200,12 +200,6 @@
     <t xml:space="preserve"> постоянное значение становится очень большим</t>
   </si>
   <si>
-    <t>Клеткоподобная равновесная устройство</t>
-  </si>
-  <si>
-    <t>Клеткоподобное равновесное устройство</t>
-  </si>
-  <si>
     <t>информация, записанная на объемной форме молекулы, способна перезаписываться</t>
   </si>
   <si>
@@ -1241,9 +1235,6 @@
     <t>обстановка постепенно начала</t>
   </si>
   <si>
-    <t>современное врачевание попыталось</t>
-  </si>
-  <si>
     <t>сделав врачевание себе прислугой</t>
   </si>
   <si>
@@ -1331,12 +1322,6 @@
     <t>из накопленного опыта Учреждения</t>
   </si>
   <si>
-    <t>посетители нашего Центра</t>
-  </si>
-  <si>
-    <t>посетители нашего Учреждения</t>
-  </si>
-  <si>
     <t>пришедшего в Центр</t>
   </si>
   <si>
@@ -2253,6 +2238,12 @@
   </si>
   <si>
     <t>сведения, записанные на объёмном образе частицы, способны перезаписываться</t>
+  </si>
+  <si>
+    <t>Клеткоподобная равновесная структура</t>
+  </si>
+  <si>
+    <t>Клетко-подобное равно-весное устройство</t>
   </si>
 </sst>
 </file>
@@ -2606,394 +2597,394 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B40" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -3047,135 +3038,135 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B14" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="B15" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B16" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B17" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B18" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -3194,42 +3185,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B5" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -3239,7 +3230,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3248,10 +3239,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B1" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -3264,432 +3255,817 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>728</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
+      <c r="A4" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>520</v>
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>650</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>638</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>410</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>413</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>724</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>489</v>
+      </c>
+      <c r="B14" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
+        <v>553</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>217</v>
+        <v>574</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>494</v>
+        <v>626</v>
       </c>
       <c r="B17" t="s">
-        <v>495</v>
+        <v>627</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>149</v>
+        <v>612</v>
+      </c>
+      <c r="B21" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>565</v>
+      </c>
+      <c r="B22" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>689</v>
+      </c>
+      <c r="B23" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>525</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>526</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>530</v>
+        <v>618</v>
       </c>
       <c r="B26" t="s">
-        <v>531</v>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B27" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>589</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>503</v>
+        <v>693</v>
       </c>
       <c r="B30" t="s">
-        <v>584</v>
+        <v>694</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>501</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>502</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="B32" t="s">
-        <v>507</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>506</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>507</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>511</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>512</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>521</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>522</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>526</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>527</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>192</v>
+        <v>549</v>
       </c>
       <c r="B40" t="s">
-        <v>193</v>
+        <v>550</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>492</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>493</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>487</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>488</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>365</v>
+        <v>193</v>
       </c>
       <c r="B43" t="s">
-        <v>366</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>642</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>643</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>282</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>283</v>
+        <v>363</v>
+      </c>
+      <c r="B45" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>331</v>
+        <v>231</v>
       </c>
       <c r="B46" t="s">
-        <v>332</v>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>532</v>
+        <v>714</v>
       </c>
       <c r="B48" t="s">
-        <v>234</v>
+        <v>715</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>554</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>558</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>570</v>
-      </c>
-      <c r="B51" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>579</v>
-      </c>
-      <c r="B52" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>594</v>
-      </c>
-      <c r="B53" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>617</v>
-      </c>
-      <c r="B54" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>623</v>
-      </c>
-      <c r="B55" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>631</v>
-      </c>
-      <c r="B56" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>643</v>
-      </c>
-      <c r="B57" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>647</v>
-      </c>
-      <c r="B58" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>655</v>
-      </c>
-      <c r="B59" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>657</v>
-      </c>
-      <c r="B60" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>694</v>
-      </c>
-      <c r="B61" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>698</v>
-      </c>
-      <c r="B62" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>719</v>
-      </c>
-      <c r="B63" t="s">
-        <v>720</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B62" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B49">
-    <sortCondition ref="A1:A49"/>
+  <autoFilter ref="A1:B61" xr:uid="{FAFFA28B-18D8-4C25-94AE-572E878ED2DD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B62">
+    <sortCondition ref="A1:A62"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C61"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="65.36328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="77.36328125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>652</v>
+      </c>
+      <c r="B22" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B59" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B61">
+    <sortCondition ref="A1:A61"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F429BA-9463-41C0-94A8-3DCD50C49D17}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="53.90625" customWidth="1"/>
@@ -3706,26 +4082,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -3738,58 +4114,58 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -3802,10 +4178,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -3816,408 +4192,23 @@
         <v>35</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="65.36328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="77.36328125" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B60" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B62">
-    <sortCondition ref="A1:A62"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4233,210 +4224,210 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B1" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B3" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B4" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B5" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B7" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B8" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B9" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B10" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B11" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B12" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B13" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B14" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B15" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B16" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="B17" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B18" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B19" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B20" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B21" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B22" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B23" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -4455,34 +4446,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -4492,7 +4483,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}">
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="43.1796875" style="3" customWidth="1"/>
@@ -4501,1080 +4492,1064 @@
   <sheetData>
     <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>405</v>
+        <v>447</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>406</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>453</v>
+        <v>721</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>726</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>472</v>
+      <c r="A35" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>473</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="6" t="s">
-        <v>291</v>
+      <c r="A36" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>381</v>
+        <v>449</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>454</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>229</v>
+        <v>432</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>588</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>377</v>
+        <v>73</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>378</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>75</v>
+        <v>483</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>76</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>488</v>
+        <v>398</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>401</v>
+        <v>178</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>423</v>
+        <v>100</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>424</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>102</v>
+        <v>278</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>103</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>280</v>
+        <v>359</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>281</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>362</v>
+        <v>150</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>50</v>
+        <v>443</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>732</v>
+        <v>444</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>477</v>
+        <v>353</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>355</v>
+        <v>428</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>356</v>
+        <v>429</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>433</v>
+        <v>391</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>434</v>
+        <v>495</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>500</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>496</v>
-      </c>
-      <c r="B62" t="s">
-        <v>497</v>
+      <c r="A61" t="s">
+        <v>491</v>
+      </c>
+      <c r="B61" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>523</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="B66" s="3" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>186</v>
+        <v>499</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>589</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>504</v>
+        <v>404</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>505</v>
+        <v>405</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>407</v>
+        <v>148</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>408</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>150</v>
+        <v>283</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>285</v>
+        <v>691</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
-        <v>696</v>
+        <v>165</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
-        <v>227</v>
+        <v>154</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
-        <v>156</v>
+        <v>453</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
-        <v>373</v>
+        <v>98</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
-        <v>93</v>
+        <v>430</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>94</v>
+        <v>431</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
-        <v>435</v>
+        <v>17</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>436</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="28.5" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
-        <v>158</v>
+        <v>512</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
-        <v>513</v>
+        <v>474</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>514</v>
+        <v>718</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
-        <v>425</v>
+        <v>660</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
-        <v>665</v>
+        <v>158</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A94" s="7" t="s">
-        <v>701</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
-        <v>160</v>
+        <v>422</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>161</v>
+        <v>423</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
-        <v>123</v>
+        <v>699</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>590</v>
+        <v>698</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
-        <v>427</v>
+        <v>470</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
-        <v>704</v>
+        <v>481</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>703</v>
+        <v>482</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
-        <v>475</v>
+        <v>145</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
-        <v>486</v>
+        <v>171</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>487</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A102" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>174</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>498</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>131</v>
+        <v>426</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>432</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>722</v>
+        <v>72</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
-        <v>508</v>
+        <v>383</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>509</v>
+        <v>384</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>73</v>
+        <v>334</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>74</v>
+        <v>335</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>386</v>
+        <v>78</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>115</v>
+        <v>220</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
-        <v>304</v>
+        <v>389</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" ht="42.5" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>223</v>
+        <v>110</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
-        <v>391</v>
+        <v>144</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>392</v>
+        <v>143</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
-        <v>146</v>
+        <v>441</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>145</v>
+        <v>442</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
-        <v>289</v>
+        <v>461</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>290</v>
+        <v>462</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
-        <v>490</v>
+        <v>336</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>491</v>
+        <v>337</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
-        <v>502</v>
+        <v>49</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
-        <v>338</v>
+        <v>457</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>731</v>
+        <v>68</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>462</v>
+        <v>75</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A133" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A134" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B137" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B137">
-    <sortCondition ref="A1:A137"/>
+  <autoFilter ref="A1:B135" xr:uid="{76086DBA-3211-4065-B947-899E870A34B7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B132">
+    <sortCondition ref="A1:A132"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5582,7 +5557,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9E41E9-C4FF-4A2E-9387-ABCBB02BFCB3}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="68.08984375" customWidth="1"/>
@@ -5591,162 +5566,170 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B1" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B3" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B4" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B5" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B6" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B7" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B8" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B9" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B10" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B11" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="B12" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B13" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B14" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B15" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B16" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="B17" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -5761,7 +5744,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
